--- a/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
+++ b/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1395.488582546247</v>
+        <v>1723.267451217869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4234978678985639</v>
+        <v>0.4762435335059165</v>
       </c>
       <c r="F2" t="n">
-        <v>453.0713144705114</v>
+        <v>439.4193276640641</v>
       </c>
       <c r="G2" t="n">
-        <v>56.1685876973978</v>
+        <v>52.83370874146046</v>
       </c>
       <c r="H2" t="n">
-        <v>1179.0743</v>
+        <v>984.4728</v>
       </c>
     </row>
     <row r="3">
@@ -502,22 +502,22 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>1396.42017850531</v>
+        <v>1728.950459284355</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4237805852975742</v>
+        <v>0.4778140940365024</v>
       </c>
       <c r="F3" t="n">
-        <v>453.782484025396</v>
+        <v>439.3296100409128</v>
       </c>
       <c r="G3" t="n">
-        <v>56.89579628620309</v>
+        <v>53.26589142884749</v>
       </c>
       <c r="H3" t="n">
-        <v>993.3964</v>
+        <v>837.6357</v>
       </c>
     </row>
     <row r="4">
@@ -528,22 +528,22 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>1403.311374423166</v>
+        <v>1761.331187680383</v>
       </c>
       <c r="E4" t="n">
-        <v>0.425871900708524</v>
+        <v>0.4867628573279584</v>
       </c>
       <c r="F4" t="n">
-        <v>452.6707192557101</v>
+        <v>441.5117300156499</v>
       </c>
       <c r="G4" t="n">
-        <v>56.17273559199003</v>
+        <v>53.42096478776056</v>
       </c>
       <c r="H4" t="n">
-        <v>997.1937</v>
+        <v>837.4529</v>
       </c>
     </row>
     <row r="5">
@@ -554,22 +554,74 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1773.48616084326</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4901220151677163</v>
+      </c>
+      <c r="F5" t="n">
+        <v>442.6019133605673</v>
+      </c>
+      <c r="G5" t="n">
+        <v>53.05125299439946</v>
+      </c>
+      <c r="H5" t="n">
+        <v>974.4356</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
         <v>18</v>
       </c>
-      <c r="D5" t="n">
-        <v>1405.595243472803</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.4265650010929901</v>
-      </c>
-      <c r="F5" t="n">
-        <v>451.6494217988279</v>
-      </c>
-      <c r="G5" t="n">
-        <v>56.59204428512697</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1178.6524</v>
+      <c r="D6" t="n">
+        <v>1792.643047632629</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4954162273047205</v>
+      </c>
+      <c r="F6" t="n">
+        <v>440.485845747803</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50.75409421054676</v>
+      </c>
+      <c r="H6" t="n">
+        <v>975.0526</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1796.920731520437</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4965984113519566</v>
+      </c>
+      <c r="F7" t="n">
+        <v>441.825887573662</v>
+      </c>
+      <c r="G7" t="n">
+        <v>51.21165593459066</v>
+      </c>
+      <c r="H7" t="n">
+        <v>837.0247000000001</v>
       </c>
     </row>
   </sheetData>
@@ -583,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,28 +685,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1393.929965248138</v>
+        <v>1599.503818777609</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4230248643133861</v>
+        <v>0.442040119757678</v>
       </c>
       <c r="G2" t="n">
-        <v>461.9029730647935</v>
+        <v>434.6914419571065</v>
       </c>
       <c r="H2" t="n">
-        <v>62.84160722575228</v>
+        <v>52.27919078260592</v>
       </c>
       <c r="I2" t="n">
-        <v>1179.0743</v>
+        <v>837.6357</v>
       </c>
     </row>
     <row r="3">
@@ -662,28 +714,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1395.787189075255</v>
+        <v>1606.969128631615</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4235884879365615</v>
+        <v>0.4441032385968784</v>
       </c>
       <c r="G3" t="n">
-        <v>462.8138423861577</v>
+        <v>435.8173494622246</v>
       </c>
       <c r="H3" t="n">
-        <v>62.86467035868183</v>
+        <v>51.83981259808937</v>
       </c>
       <c r="I3" t="n">
-        <v>993.3964</v>
+        <v>984.4728</v>
       </c>
     </row>
     <row r="4">
@@ -691,28 +743,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1404.290985687591</v>
+        <v>1656.106205406015</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4261691896201225</v>
+        <v>0.4576827993624775</v>
       </c>
       <c r="G4" t="n">
-        <v>454.6122363223529</v>
+        <v>437.651219973989</v>
       </c>
       <c r="H4" t="n">
-        <v>58.94155831545768</v>
+        <v>52.09846348965927</v>
       </c>
       <c r="I4" t="n">
-        <v>1178.6524</v>
+        <v>837.4529</v>
       </c>
     </row>
     <row r="5">
@@ -720,28 +772,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>0.55</v>
       </c>
       <c r="E5" t="n">
-        <v>1405.258294040459</v>
+        <v>1657.631874178728</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4264627448882656</v>
+        <v>0.4581044343714618</v>
       </c>
       <c r="G5" t="n">
-        <v>460.2335498764342</v>
+        <v>427.3678013566716</v>
       </c>
       <c r="H5" t="n">
-        <v>60.47755125651768</v>
+        <v>47.64618322755457</v>
       </c>
       <c r="I5" t="n">
-        <v>1179.0743</v>
+        <v>837.6357</v>
       </c>
     </row>
     <row r="6">
@@ -752,25 +804,25 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E6" t="n">
-        <v>1406.937112632886</v>
+        <v>1658.897586864472</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4269722267309505</v>
+        <v>0.4584542277140074</v>
       </c>
       <c r="G6" t="n">
-        <v>455.6941899428435</v>
+        <v>427.5855705146135</v>
       </c>
       <c r="H6" t="n">
-        <v>53.81169637476948</v>
+        <v>47.27452516123537</v>
       </c>
       <c r="I6" t="n">
-        <v>1179.0743</v>
+        <v>984.4728</v>
       </c>
     </row>
     <row r="7">
@@ -781,25 +833,25 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1407.053238552197</v>
+        <v>1674.236534576459</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4270074682082734</v>
+        <v>0.4626933112372624</v>
       </c>
       <c r="G7" t="n">
-        <v>458.6529236112696</v>
+        <v>440.4528319744873</v>
       </c>
       <c r="H7" t="n">
-        <v>61.19737908027424</v>
+        <v>51.81145545773027</v>
       </c>
       <c r="I7" t="n">
-        <v>1178.6524</v>
+        <v>974.4356</v>
       </c>
     </row>
     <row r="8">
@@ -810,25 +862,25 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1407.797927478321</v>
+        <v>1690.398631983192</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4272334637315658</v>
+        <v>0.4671598810505607</v>
       </c>
       <c r="G8" t="n">
-        <v>447.4611539021552</v>
+        <v>426.3600916312859</v>
       </c>
       <c r="H8" t="n">
-        <v>50.99829137836364</v>
+        <v>43.38381582897451</v>
       </c>
       <c r="I8" t="n">
-        <v>1178.6524</v>
+        <v>984.4728</v>
       </c>
     </row>
     <row r="9">
@@ -836,28 +888,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1407.932068050039</v>
+        <v>1690.728978533481</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4272741722309628</v>
+        <v>0.4672511758802055</v>
       </c>
       <c r="G9" t="n">
-        <v>451.6888802543323</v>
+        <v>427.2500854495922</v>
       </c>
       <c r="H9" t="n">
-        <v>54.91777174322506</v>
+        <v>43.74693319680208</v>
       </c>
       <c r="I9" t="n">
-        <v>1178.6524</v>
+        <v>837.6357</v>
       </c>
     </row>
     <row r="10">
@@ -874,19 +926,19 @@
         <v>0.55</v>
       </c>
       <c r="E10" t="n">
-        <v>1408.039980343929</v>
+        <v>1696.840834517214</v>
       </c>
       <c r="F10" t="n">
-        <v>0.427306921066714</v>
+        <v>0.4689402531548417</v>
       </c>
       <c r="G10" t="n">
-        <v>461.2355824276953</v>
+        <v>427.8527680828596</v>
       </c>
       <c r="H10" t="n">
-        <v>60.38828661575783</v>
+        <v>47.54152459831126</v>
       </c>
       <c r="I10" t="n">
-        <v>993.3964</v>
+        <v>837.4529</v>
       </c>
     </row>
     <row r="11">
@@ -894,28 +946,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E11" t="n">
-        <v>1409.429008514404</v>
+        <v>1710.457358884526</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4277284583519377</v>
+        <v>0.4727033264225316</v>
       </c>
       <c r="G11" t="n">
-        <v>456.5373100886807</v>
+        <v>430.4979187610977</v>
       </c>
       <c r="H11" t="n">
-        <v>53.63719015934706</v>
+        <v>47.24751112409809</v>
       </c>
       <c r="I11" t="n">
-        <v>993.3964</v>
+        <v>974.4356</v>
       </c>
     </row>
     <row r="12">
@@ -923,28 +975,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1412.771567394752</v>
+        <v>1736.229786203676</v>
       </c>
       <c r="F12" t="n">
-        <v>0.428742846127558</v>
+        <v>0.4798258144871801</v>
       </c>
       <c r="G12" t="n">
-        <v>451.6822444290898</v>
+        <v>426.4287566540011</v>
       </c>
       <c r="H12" t="n">
-        <v>51.27633320297015</v>
+        <v>43.42155900394563</v>
       </c>
       <c r="I12" t="n">
-        <v>1179.0743</v>
+        <v>837.4529</v>
       </c>
     </row>
     <row r="13">
@@ -955,25 +1007,25 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E13" t="n">
-        <v>1413.637357990712</v>
+        <v>1739.780245886782</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4290055931510893</v>
+        <v>0.4808070222874305</v>
       </c>
       <c r="G13" t="n">
-        <v>445.2001752622678</v>
+        <v>429.4702812506588</v>
       </c>
       <c r="H13" t="n">
-        <v>47.82814876069195</v>
+        <v>40.67734426660005</v>
       </c>
       <c r="I13" t="n">
-        <v>1178.6524</v>
+        <v>984.4728</v>
       </c>
     </row>
     <row r="14">
@@ -984,25 +1036,25 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
         <v>0.45</v>
       </c>
       <c r="E14" t="n">
-        <v>1415.297942934025</v>
+        <v>1742.053476923684</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4295095415113648</v>
+        <v>0.4814352541853431</v>
       </c>
       <c r="G14" t="n">
-        <v>448.8219878697666</v>
+        <v>430.1882649605262</v>
       </c>
       <c r="H14" t="n">
-        <v>51.04655134640325</v>
+        <v>41.01910963202392</v>
       </c>
       <c r="I14" t="n">
-        <v>997.1937</v>
+        <v>837.6357</v>
       </c>
     </row>
     <row r="15">
@@ -1010,28 +1062,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1415.472888751441</v>
+        <v>1750.899868058372</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4295626334403136</v>
+        <v>0.4838800497217421</v>
       </c>
       <c r="G15" t="n">
-        <v>455.6849088873801</v>
+        <v>428.0719168395265</v>
       </c>
       <c r="H15" t="n">
-        <v>58.84441045482161</v>
+        <v>43.19577249943573</v>
       </c>
       <c r="I15" t="n">
-        <v>997.1937</v>
+        <v>974.4356</v>
       </c>
     </row>
     <row r="16">
@@ -1039,28 +1091,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>1415.490322377586</v>
+        <v>1759.337296272204</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4295679241346228</v>
+        <v>0.4862118239471637</v>
       </c>
       <c r="G16" t="n">
-        <v>452.3676130146112</v>
+        <v>441.4597181389412</v>
       </c>
       <c r="H16" t="n">
-        <v>51.31814584282791</v>
+        <v>49.74134318246772</v>
       </c>
       <c r="I16" t="n">
-        <v>993.3964</v>
+        <v>975.0526</v>
       </c>
     </row>
     <row r="17">
@@ -1074,22 +1126,22 @@
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E17" t="n">
-        <v>1416.712155715869</v>
+        <v>1762.359171538601</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4299387217320823</v>
+        <v>0.4870469517467782</v>
       </c>
       <c r="G17" t="n">
-        <v>448.2399310554177</v>
+        <v>428.1838648124625</v>
       </c>
       <c r="H17" t="n">
-        <v>46.13936661104768</v>
+        <v>40.69005468142417</v>
       </c>
       <c r="I17" t="n">
-        <v>993.3964</v>
+        <v>837.4529</v>
       </c>
     </row>
     <row r="18">
@@ -1097,28 +1149,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E18" t="n">
-        <v>1416.979302462677</v>
+        <v>1764.238050680514</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4300197944682583</v>
+        <v>0.4875662002481891</v>
       </c>
       <c r="G18" t="n">
-        <v>447.8259724084528</v>
+        <v>442.4219492415288</v>
       </c>
       <c r="H18" t="n">
-        <v>46.19274204686363</v>
+        <v>50.09103339404626</v>
       </c>
       <c r="I18" t="n">
-        <v>1179.0743</v>
+        <v>837.0247000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1126,28 +1178,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E19" t="n">
-        <v>1418.95331139031</v>
+        <v>1781.204058694228</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4306188596147031</v>
+        <v>0.4922549394222686</v>
       </c>
       <c r="G19" t="n">
-        <v>453.0338697812325</v>
+        <v>429.7977400615819</v>
       </c>
       <c r="H19" t="n">
-        <v>54.92882414199396</v>
+        <v>40.51217517628555</v>
       </c>
       <c r="I19" t="n">
-        <v>997.1937</v>
+        <v>974.4356</v>
       </c>
     </row>
     <row r="20">
@@ -1155,28 +1207,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="E20" t="n">
-        <v>1422.369150548293</v>
+        <v>1798.443777984519</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4316554862260442</v>
+        <v>0.4970193216576876</v>
       </c>
       <c r="G20" t="n">
-        <v>446.5092209103768</v>
+        <v>432.7129927703778</v>
       </c>
       <c r="H20" t="n">
-        <v>47.87322548635468</v>
+        <v>45.89322017784767</v>
       </c>
       <c r="I20" t="n">
-        <v>997.1937</v>
+        <v>975.0526</v>
       </c>
     </row>
     <row r="21">
@@ -1190,22 +1242,312 @@
         <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E21" t="n">
-        <v>1422.689501125008</v>
+        <v>1799.549596945013</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4317527050696204</v>
+        <v>0.4973249266459274</v>
       </c>
       <c r="G21" t="n">
-        <v>460.1783008951912</v>
+        <v>433.1928208972801</v>
       </c>
       <c r="H21" t="n">
-        <v>61.11933770808857</v>
+        <v>46.15329885461609</v>
       </c>
       <c r="I21" t="n">
-        <v>997.1937</v>
+        <v>837.0247000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1826.13977181382</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5046734080595996</v>
+      </c>
+      <c r="G22" t="n">
+        <v>428.1891776955242</v>
+      </c>
+      <c r="H22" t="n">
+        <v>41.96591697722917</v>
+      </c>
+      <c r="I22" t="n">
+        <v>975.0526</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1826.165624788645</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5046805528078357</v>
+      </c>
+      <c r="G23" t="n">
+        <v>429.1750389529183</v>
+      </c>
+      <c r="H23" t="n">
+        <v>42.2497038074865</v>
+      </c>
+      <c r="I23" t="n">
+        <v>837.0247000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1853.821711146805</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5123236103499754</v>
+      </c>
+      <c r="G24" t="n">
+        <v>441.325381997354</v>
+      </c>
+      <c r="H24" t="n">
+        <v>38.68861490219472</v>
+      </c>
+      <c r="I24" t="n">
+        <v>984.4728</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1856.406518973018</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5130379498517862</v>
+      </c>
+      <c r="G25" t="n">
+        <v>429.6284280222555</v>
+      </c>
+      <c r="H25" t="n">
+        <v>39.88621623924967</v>
+      </c>
+      <c r="I25" t="n">
+        <v>837.0247000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1857.942470958255</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5134624267373838</v>
+      </c>
+      <c r="G26" t="n">
+        <v>428.4450139347466</v>
+      </c>
+      <c r="H26" t="n">
+        <v>39.48084173262465</v>
+      </c>
+      <c r="I26" t="n">
+        <v>975.0526</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1858.612963044279</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5136477244519144</v>
+      </c>
+      <c r="G27" t="n">
+        <v>442.4616338614094</v>
+      </c>
+      <c r="H27" t="n">
+        <v>38.97994107455117</v>
+      </c>
+      <c r="I27" t="n">
+        <v>837.6357</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>15</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1861.918981834317</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.5145613783767838</v>
+      </c>
+      <c r="G28" t="n">
+        <v>438.8243848438888</v>
+      </c>
+      <c r="H28" t="n">
+        <v>39.12195505624732</v>
+      </c>
+      <c r="I28" t="n">
+        <v>837.4529</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1875.088563272061</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5182009341487405</v>
+      </c>
+      <c r="G29" t="n">
+        <v>440.2649519763665</v>
+      </c>
+      <c r="H29" t="n">
+        <v>38.85176260585988</v>
+      </c>
+      <c r="I29" t="n">
+        <v>974.4356</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" t="n">
+        <v>18</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1888.566430369247</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5219256879853842</v>
+      </c>
+      <c r="G30" t="n">
+        <v>435.3440207260993</v>
+      </c>
+      <c r="H30" t="n">
+        <v>37.70565219301954</v>
+      </c>
+      <c r="I30" t="n">
+        <v>837.0247000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" t="n">
+        <v>18</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1889.32049415609</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5221340816401713</v>
+      </c>
+      <c r="G31" t="n">
+        <v>433.799147909185</v>
+      </c>
+      <c r="H31" t="n">
+        <v>37.26431138461177</v>
+      </c>
+      <c r="I31" t="n">
+        <v>975.0526</v>
       </c>
     </row>
   </sheetData>
@@ -1267,22 +1609,22 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1395.488582546247</v>
+        <v>1723.267451217869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4234978678985639</v>
+        <v>0.4762435335059165</v>
       </c>
       <c r="F2" t="n">
-        <v>453.0713144705114</v>
+        <v>439.4193276640641</v>
       </c>
       <c r="G2" t="n">
-        <v>56.1685876973978</v>
+        <v>52.83370874146046</v>
       </c>
       <c r="H2" t="n">
-        <v>1179.0743</v>
+        <v>984.4728</v>
       </c>
     </row>
   </sheetData>
@@ -1346,28 +1688,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1393.929965248138</v>
+        <v>1599.503818777609</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4230248643133861</v>
+        <v>0.442040119757678</v>
       </c>
       <c r="G2" t="n">
-        <v>461.9029730647935</v>
+        <v>434.6914419571065</v>
       </c>
       <c r="H2" t="n">
-        <v>62.84160722575228</v>
+        <v>52.27919078260592</v>
       </c>
       <c r="I2" t="n">
-        <v>1179.0743</v>
+        <v>837.6357</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
+++ b/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,25 +473,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1723.267451217869</v>
+        <v>1679.657511378417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4762435335059165</v>
+        <v>0.4641914566037251</v>
       </c>
       <c r="F2" t="n">
-        <v>439.4193276640641</v>
+        <v>443.4065354497588</v>
       </c>
       <c r="G2" t="n">
-        <v>52.83370874146046</v>
+        <v>56.69277432394815</v>
       </c>
       <c r="H2" t="n">
-        <v>984.4728</v>
+        <v>219.5934</v>
       </c>
     </row>
     <row r="3">
@@ -499,25 +499,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>1728.950459284355</v>
+        <v>1683.917057054794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4778140940365024</v>
+        <v>0.465368627960739</v>
       </c>
       <c r="F3" t="n">
-        <v>439.3296100409128</v>
+        <v>450.6986365662745</v>
       </c>
       <c r="G3" t="n">
-        <v>53.26589142884749</v>
+        <v>60.07133167456824</v>
       </c>
       <c r="H3" t="n">
-        <v>837.6357</v>
+        <v>147.552</v>
       </c>
     </row>
     <row r="4">
@@ -525,25 +525,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>1761.331187680383</v>
+        <v>1805.979684291212</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4867628573279584</v>
+        <v>0.4991019505874759</v>
       </c>
       <c r="F4" t="n">
-        <v>441.5117300156499</v>
+        <v>449.9125232318023</v>
       </c>
       <c r="G4" t="n">
-        <v>53.42096478776056</v>
+        <v>57.65099365604187</v>
       </c>
       <c r="H4" t="n">
-        <v>837.4529</v>
+        <v>217.5576</v>
       </c>
     </row>
     <row r="5">
@@ -551,77 +551,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1773.48616084326</v>
+        <v>1853.254451438969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4901220151677163</v>
+        <v>0.5121668420157948</v>
       </c>
       <c r="F5" t="n">
-        <v>442.6019133605673</v>
+        <v>455.7159378028213</v>
       </c>
       <c r="G5" t="n">
-        <v>53.05125299439946</v>
+        <v>59.95635304595971</v>
       </c>
       <c r="H5" t="n">
-        <v>974.4356</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1792.643047632629</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.4954162273047205</v>
-      </c>
-      <c r="F6" t="n">
-        <v>440.485845747803</v>
-      </c>
-      <c r="G6" t="n">
-        <v>50.75409421054676</v>
-      </c>
-      <c r="H6" t="n">
-        <v>975.0526</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1796.920731520437</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.4965984113519566</v>
-      </c>
-      <c r="F7" t="n">
-        <v>441.825887573662</v>
-      </c>
-      <c r="G7" t="n">
-        <v>51.21165593459066</v>
-      </c>
-      <c r="H7" t="n">
-        <v>837.0247000000001</v>
+        <v>147.5415</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -694,19 +642,19 @@
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1599.503818777609</v>
+        <v>1503.986624119089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.442040119757678</v>
+        <v>0.4156429135302885</v>
       </c>
       <c r="G2" t="n">
-        <v>434.6914419571065</v>
+        <v>437.5559240462001</v>
       </c>
       <c r="H2" t="n">
-        <v>52.27919078260592</v>
+        <v>54.14836824382113</v>
       </c>
       <c r="I2" t="n">
-        <v>837.6357</v>
+        <v>219.5934</v>
       </c>
     </row>
     <row r="3">
@@ -714,7 +662,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
@@ -723,19 +671,19 @@
         <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1606.969128631615</v>
+        <v>1528.367594088505</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4441032385968784</v>
+        <v>0.4223808573592227</v>
       </c>
       <c r="G3" t="n">
-        <v>435.8173494622246</v>
+        <v>443.5444838571186</v>
       </c>
       <c r="H3" t="n">
-        <v>51.83981259808937</v>
+        <v>55.40369064530769</v>
       </c>
       <c r="I3" t="n">
-        <v>984.4728</v>
+        <v>147.552</v>
       </c>
     </row>
     <row r="4">
@@ -743,28 +691,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>1656.106205406015</v>
+        <v>1591.013377821525</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4576827993624775</v>
+        <v>0.4396936948895642</v>
       </c>
       <c r="G4" t="n">
-        <v>437.651219973989</v>
+        <v>431.6820492557358</v>
       </c>
       <c r="H4" t="n">
-        <v>52.09846348965927</v>
+        <v>49.83849257834829</v>
       </c>
       <c r="I4" t="n">
-        <v>837.4529</v>
+        <v>219.5934</v>
       </c>
     </row>
     <row r="5">
@@ -772,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>16</v>
@@ -781,19 +729,19 @@
         <v>0.55</v>
       </c>
       <c r="E5" t="n">
-        <v>1657.631874178728</v>
+        <v>1607.989123747605</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4581044343714618</v>
+        <v>0.444385125240681</v>
       </c>
       <c r="G5" t="n">
-        <v>427.3678013566716</v>
+        <v>439.2611362045692</v>
       </c>
       <c r="H5" t="n">
-        <v>47.64618322755457</v>
+        <v>51.13909183200884</v>
       </c>
       <c r="I5" t="n">
-        <v>837.6357</v>
+        <v>147.552</v>
       </c>
     </row>
     <row r="6">
@@ -801,28 +749,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1658.897586864472</v>
+        <v>1631.631136735541</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4584542277140074</v>
+        <v>0.450918850343311</v>
       </c>
       <c r="G6" t="n">
-        <v>427.5855705146135</v>
+        <v>431.7982730992577</v>
       </c>
       <c r="H6" t="n">
-        <v>47.27452516123537</v>
+        <v>45.8843601575164</v>
       </c>
       <c r="I6" t="n">
-        <v>984.4728</v>
+        <v>219.5934</v>
       </c>
     </row>
     <row r="7">
@@ -830,28 +778,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1674.236534576459</v>
+        <v>1633.086596741191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4626933112372624</v>
+        <v>0.451321082402808</v>
       </c>
       <c r="G7" t="n">
-        <v>440.4528319744873</v>
+        <v>438.7302081093948</v>
       </c>
       <c r="H7" t="n">
-        <v>51.81145545773027</v>
+        <v>47.39375280600772</v>
       </c>
       <c r="I7" t="n">
-        <v>974.4356</v>
+        <v>147.552</v>
       </c>
     </row>
     <row r="8">
@@ -859,28 +807,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E8" t="n">
-        <v>1690.398631983192</v>
+        <v>1648.948423684333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4671598810505607</v>
+        <v>0.4557046692371803</v>
       </c>
       <c r="G8" t="n">
-        <v>426.3600916312859</v>
+        <v>438.872634378338</v>
       </c>
       <c r="H8" t="n">
-        <v>43.38381582897451</v>
+        <v>45.01407061321417</v>
       </c>
       <c r="I8" t="n">
-        <v>984.4728</v>
+        <v>147.552</v>
       </c>
     </row>
     <row r="9">
@@ -888,28 +836,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E9" t="n">
-        <v>1690.728978533481</v>
+        <v>1659.956956331859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4672511758802055</v>
+        <v>0.4587469958841949</v>
       </c>
       <c r="G9" t="n">
-        <v>427.2500854495922</v>
+        <v>432.219916597818</v>
       </c>
       <c r="H9" t="n">
-        <v>43.74693319680208</v>
+        <v>43.43671413955228</v>
       </c>
       <c r="I9" t="n">
-        <v>837.6357</v>
+        <v>219.5934</v>
       </c>
     </row>
     <row r="10">
@@ -917,28 +865,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
-        <v>1696.840834517214</v>
+        <v>1702.472323352153</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4689402531548417</v>
+        <v>0.4704965757905156</v>
       </c>
       <c r="G10" t="n">
-        <v>427.8527680828596</v>
+        <v>447.5223518980079</v>
       </c>
       <c r="H10" t="n">
-        <v>47.54152459831126</v>
+        <v>54.4633808994751</v>
       </c>
       <c r="I10" t="n">
-        <v>837.4529</v>
+        <v>217.5576</v>
       </c>
     </row>
     <row r="11">
@@ -946,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>15</v>
@@ -955,19 +903,19 @@
         <v>0.55</v>
       </c>
       <c r="E11" t="n">
-        <v>1710.457358884526</v>
+        <v>1724.527858515831</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4727033264225316</v>
+        <v>0.4765918606473672</v>
       </c>
       <c r="G11" t="n">
-        <v>430.4979187610977</v>
+        <v>435.7953017284703</v>
       </c>
       <c r="H11" t="n">
-        <v>47.24751112409809</v>
+        <v>49.72847177241587</v>
       </c>
       <c r="I11" t="n">
-        <v>974.4356</v>
+        <v>217.5576</v>
       </c>
     </row>
     <row r="12">
@@ -975,7 +923,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
@@ -984,19 +932,19 @@
         <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1736.229786203676</v>
+        <v>1753.758233678002</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4798258144871801</v>
+        <v>0.4846699898681671</v>
       </c>
       <c r="G12" t="n">
-        <v>426.4287566540011</v>
+        <v>433.0485126176067</v>
       </c>
       <c r="H12" t="n">
-        <v>43.42155900394563</v>
+        <v>46.20989273272708</v>
       </c>
       <c r="I12" t="n">
-        <v>837.4529</v>
+        <v>217.5576</v>
       </c>
     </row>
     <row r="13">
@@ -1004,28 +952,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>1739.780245886782</v>
+        <v>1767.188843747391</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4808070222874305</v>
+        <v>0.4883816837158431</v>
       </c>
       <c r="G13" t="n">
-        <v>429.4702812506588</v>
+        <v>455.0782437949665</v>
       </c>
       <c r="H13" t="n">
-        <v>40.67734426660005</v>
+        <v>55.87042245390593</v>
       </c>
       <c r="I13" t="n">
-        <v>984.4728</v>
+        <v>147.5415</v>
       </c>
     </row>
     <row r="14">
@@ -1033,28 +981,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E14" t="n">
-        <v>1742.053476923684</v>
+        <v>1771.729311254256</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4814352541853431</v>
+        <v>0.4896364908484852</v>
       </c>
       <c r="G14" t="n">
-        <v>430.1882649605262</v>
+        <v>442.2057534790958</v>
       </c>
       <c r="H14" t="n">
-        <v>41.01910963202392</v>
+        <v>50.99486042213588</v>
       </c>
       <c r="I14" t="n">
-        <v>837.6357</v>
+        <v>147.5415</v>
       </c>
     </row>
     <row r="15">
@@ -1062,28 +1010,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
         <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E15" t="n">
-        <v>1750.899868058372</v>
+        <v>1771.807743712938</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4838800497217421</v>
+        <v>0.4896581665037864</v>
       </c>
       <c r="G15" t="n">
-        <v>428.0719168395265</v>
+        <v>434.1713581668672</v>
       </c>
       <c r="H15" t="n">
-        <v>43.19577249943573</v>
+        <v>43.86609210286657</v>
       </c>
       <c r="I15" t="n">
-        <v>974.4356</v>
+        <v>217.5576</v>
       </c>
     </row>
     <row r="16">
@@ -1091,28 +1039,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1759.337296272204</v>
+        <v>1799.426968682379</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4862118239471637</v>
+        <v>0.497291037003862</v>
       </c>
       <c r="G16" t="n">
-        <v>441.4597181389412</v>
+        <v>438.517028026179</v>
       </c>
       <c r="H16" t="n">
-        <v>49.74134318246772</v>
+        <v>47.39949755777401</v>
       </c>
       <c r="I16" t="n">
-        <v>975.0526</v>
+        <v>147.5415</v>
       </c>
     </row>
     <row r="17">
@@ -1120,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1129,19 +1077,19 @@
         <v>0.45</v>
       </c>
       <c r="E17" t="n">
-        <v>1762.359171538601</v>
+        <v>1814.935537435342</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4870469517467782</v>
+        <v>0.5015769971299648</v>
       </c>
       <c r="G17" t="n">
-        <v>428.1838648124625</v>
+        <v>439.7729581060469</v>
       </c>
       <c r="H17" t="n">
-        <v>40.69005468142417</v>
+        <v>45.25632939246051</v>
       </c>
       <c r="I17" t="n">
-        <v>837.4529</v>
+        <v>147.5415</v>
       </c>
     </row>
     <row r="18">
@@ -1149,28 +1097,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>1764.238050680514</v>
+        <v>1840.266043039844</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4875662002481891</v>
+        <v>0.5085773553657418</v>
       </c>
       <c r="G18" t="n">
-        <v>442.4219492415288</v>
+        <v>444.4523567885124</v>
       </c>
       <c r="H18" t="n">
-        <v>50.09103339404626</v>
+        <v>41.53383824148825</v>
       </c>
       <c r="I18" t="n">
-        <v>837.0247000000001</v>
+        <v>219.5934</v>
       </c>
     </row>
     <row r="19">
@@ -1178,28 +1126,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>1781.204058694228</v>
+        <v>1852.796765714568</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4922549394222686</v>
+        <v>0.5120403556329237</v>
       </c>
       <c r="G19" t="n">
-        <v>429.7977400615819</v>
+        <v>452.7988090254431</v>
       </c>
       <c r="H19" t="n">
-        <v>40.51217517628555</v>
+        <v>43.10378172798949</v>
       </c>
       <c r="I19" t="n">
-        <v>974.4356</v>
+        <v>147.552</v>
       </c>
     </row>
     <row r="20">
@@ -1207,28 +1155,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>1798.443777984519</v>
+        <v>1867.190072636094</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4970193216576876</v>
+        <v>0.5160181011316264</v>
       </c>
       <c r="G20" t="n">
-        <v>432.7129927703778</v>
+        <v>442.1968949849231</v>
       </c>
       <c r="H20" t="n">
-        <v>45.89322017784767</v>
+        <v>42.31418858982504</v>
       </c>
       <c r="I20" t="n">
-        <v>975.0526</v>
+        <v>217.5576</v>
       </c>
     </row>
     <row r="21">
@@ -1236,318 +1184,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>1799.549596945013</v>
+        <v>1901.322786537956</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4973249266459274</v>
+        <v>0.5254510445005047</v>
       </c>
       <c r="G21" t="n">
-        <v>433.1928208972801</v>
+        <v>446.326401401286</v>
       </c>
       <c r="H21" t="n">
-        <v>46.15329885461609</v>
+        <v>43.39630072123119</v>
       </c>
       <c r="I21" t="n">
-        <v>837.0247000000001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="n">
-        <v>11</v>
-      </c>
-      <c r="C22" t="n">
-        <v>18</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1826.13977181382</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5046734080595996</v>
-      </c>
-      <c r="G22" t="n">
-        <v>428.1891776955242</v>
-      </c>
-      <c r="H22" t="n">
-        <v>41.96591697722917</v>
-      </c>
-      <c r="I22" t="n">
-        <v>975.0526</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="n">
-        <v>10</v>
-      </c>
-      <c r="C23" t="n">
-        <v>18</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1826.165624788645</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5046805528078357</v>
-      </c>
-      <c r="G23" t="n">
-        <v>429.1750389529183</v>
-      </c>
-      <c r="H23" t="n">
-        <v>42.2497038074865</v>
-      </c>
-      <c r="I23" t="n">
-        <v>837.0247000000001</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="n">
-        <v>11</v>
-      </c>
-      <c r="C24" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1853.821711146805</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5123236103499754</v>
-      </c>
-      <c r="G24" t="n">
-        <v>441.325381997354</v>
-      </c>
-      <c r="H24" t="n">
-        <v>38.68861490219472</v>
-      </c>
-      <c r="I24" t="n">
-        <v>984.4728</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="n">
-        <v>10</v>
-      </c>
-      <c r="C25" t="n">
-        <v>18</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1856.406518973018</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5130379498517862</v>
-      </c>
-      <c r="G25" t="n">
-        <v>429.6284280222555</v>
-      </c>
-      <c r="H25" t="n">
-        <v>39.88621623924967</v>
-      </c>
-      <c r="I25" t="n">
-        <v>837.0247000000001</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="n">
-        <v>11</v>
-      </c>
-      <c r="C26" t="n">
-        <v>18</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1857.942470958255</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5134624267373838</v>
-      </c>
-      <c r="G26" t="n">
-        <v>428.4450139347466</v>
-      </c>
-      <c r="H26" t="n">
-        <v>39.48084173262465</v>
-      </c>
-      <c r="I26" t="n">
-        <v>975.0526</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="n">
-        <v>10</v>
-      </c>
-      <c r="C27" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1858.612963044279</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5136477244519144</v>
-      </c>
-      <c r="G27" t="n">
-        <v>442.4616338614094</v>
-      </c>
-      <c r="H27" t="n">
-        <v>38.97994107455117</v>
-      </c>
-      <c r="I27" t="n">
-        <v>837.6357</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="n">
-        <v>10</v>
-      </c>
-      <c r="C28" t="n">
-        <v>15</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1861.918981834317</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5145613783767838</v>
-      </c>
-      <c r="G28" t="n">
-        <v>438.8243848438888</v>
-      </c>
-      <c r="H28" t="n">
-        <v>39.12195505624732</v>
-      </c>
-      <c r="I28" t="n">
-        <v>837.4529</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="n">
-        <v>11</v>
-      </c>
-      <c r="C29" t="n">
-        <v>15</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1875.088563272061</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.5182009341487405</v>
-      </c>
-      <c r="G29" t="n">
-        <v>440.2649519763665</v>
-      </c>
-      <c r="H29" t="n">
-        <v>38.85176260585988</v>
-      </c>
-      <c r="I29" t="n">
-        <v>974.4356</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="n">
-        <v>10</v>
-      </c>
-      <c r="C30" t="n">
-        <v>18</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1888.566430369247</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.5219256879853842</v>
-      </c>
-      <c r="G30" t="n">
-        <v>435.3440207260993</v>
-      </c>
-      <c r="H30" t="n">
-        <v>37.70565219301954</v>
-      </c>
-      <c r="I30" t="n">
-        <v>837.0247000000001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="n">
-        <v>11</v>
-      </c>
-      <c r="C31" t="n">
-        <v>18</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1889.32049415609</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.5221340816401713</v>
-      </c>
-      <c r="G31" t="n">
-        <v>433.799147909185</v>
-      </c>
-      <c r="H31" t="n">
-        <v>37.26431138461177</v>
-      </c>
-      <c r="I31" t="n">
-        <v>975.0526</v>
+        <v>147.5415</v>
       </c>
     </row>
   </sheetData>
@@ -1606,25 +1264,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1723.267451217869</v>
+        <v>1679.657511378417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4762435335059165</v>
+        <v>0.4641914566037251</v>
       </c>
       <c r="F2" t="n">
-        <v>439.4193276640641</v>
+        <v>443.4065354497588</v>
       </c>
       <c r="G2" t="n">
-        <v>52.83370874146046</v>
+        <v>56.69277432394815</v>
       </c>
       <c r="H2" t="n">
-        <v>984.4728</v>
+        <v>219.5934</v>
       </c>
     </row>
   </sheetData>
@@ -1688,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -1697,19 +1355,19 @@
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1599.503818777609</v>
+        <v>1503.986624119089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.442040119757678</v>
+        <v>0.4156429135302885</v>
       </c>
       <c r="G2" t="n">
-        <v>434.6914419571065</v>
+        <v>437.5559240462001</v>
       </c>
       <c r="H2" t="n">
-        <v>52.27919078260592</v>
+        <v>54.14836824382113</v>
       </c>
       <c r="I2" t="n">
-        <v>837.6357</v>
+        <v>219.5934</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
+++ b/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,25 +473,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1679.657511378417</v>
+        <v>1728.950459284355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4641914566037251</v>
+        <v>0.4778140940365024</v>
       </c>
       <c r="F2" t="n">
-        <v>443.4065354497588</v>
+        <v>439.3296100409128</v>
       </c>
       <c r="G2" t="n">
-        <v>56.69277432394815</v>
+        <v>53.26589142884749</v>
       </c>
       <c r="H2" t="n">
-        <v>219.5934</v>
+        <v>741.0981</v>
       </c>
     </row>
     <row r="3">
@@ -499,77 +499,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>1683.917057054794</v>
+        <v>1761.331187680383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.465368627960739</v>
+        <v>0.4867628573279584</v>
       </c>
       <c r="F3" t="n">
-        <v>450.6986365662745</v>
+        <v>441.5117300156499</v>
       </c>
       <c r="G3" t="n">
-        <v>60.07133167456824</v>
+        <v>53.42096478776056</v>
       </c>
       <c r="H3" t="n">
-        <v>147.552</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1805.979684291212</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4991019505874759</v>
-      </c>
-      <c r="F4" t="n">
-        <v>449.9125232318023</v>
-      </c>
-      <c r="G4" t="n">
-        <v>57.65099365604187</v>
-      </c>
-      <c r="H4" t="n">
-        <v>217.5576</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1853.254451438969</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.5121668420157948</v>
-      </c>
-      <c r="F5" t="n">
-        <v>455.7159378028213</v>
-      </c>
-      <c r="G5" t="n">
-        <v>59.95635304595971</v>
-      </c>
-      <c r="H5" t="n">
-        <v>147.5415</v>
+        <v>738.8771</v>
       </c>
     </row>
   </sheetData>
@@ -583,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +581,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -642,19 +590,19 @@
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1503.986624119089</v>
+        <v>1599.503818777609</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4156429135302885</v>
+        <v>0.442040119757678</v>
       </c>
       <c r="G2" t="n">
-        <v>437.5559240462001</v>
+        <v>434.6914419571065</v>
       </c>
       <c r="H2" t="n">
-        <v>54.14836824382113</v>
+        <v>52.27919078260592</v>
       </c>
       <c r="I2" t="n">
-        <v>219.5934</v>
+        <v>741.0981</v>
       </c>
     </row>
     <row r="3">
@@ -662,28 +610,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1528.367594088505</v>
+        <v>1656.106205406015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4223808573592227</v>
+        <v>0.4576827993624775</v>
       </c>
       <c r="G3" t="n">
-        <v>443.5444838571186</v>
+        <v>437.651219973989</v>
       </c>
       <c r="H3" t="n">
-        <v>55.40369064530769</v>
+        <v>52.09846348965927</v>
       </c>
       <c r="I3" t="n">
-        <v>147.552</v>
+        <v>738.8771</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +639,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>16</v>
@@ -700,19 +648,19 @@
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>1591.013377821525</v>
+        <v>1657.631874178728</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4396936948895642</v>
+        <v>0.4581044343714618</v>
       </c>
       <c r="G4" t="n">
-        <v>431.6820492557358</v>
+        <v>427.3678013566716</v>
       </c>
       <c r="H4" t="n">
-        <v>49.83849257834829</v>
+        <v>47.64618322755457</v>
       </c>
       <c r="I4" t="n">
-        <v>219.5934</v>
+        <v>741.0981</v>
       </c>
     </row>
     <row r="5">
@@ -720,28 +668,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1607.989123747605</v>
+        <v>1690.728978533481</v>
       </c>
       <c r="F5" t="n">
-        <v>0.444385125240681</v>
+        <v>0.4672511758802055</v>
       </c>
       <c r="G5" t="n">
-        <v>439.2611362045692</v>
+        <v>427.2500854495922</v>
       </c>
       <c r="H5" t="n">
-        <v>51.13909183200884</v>
+        <v>43.74693319680208</v>
       </c>
       <c r="I5" t="n">
-        <v>147.552</v>
+        <v>741.0981</v>
       </c>
     </row>
     <row r="6">
@@ -749,28 +697,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E6" t="n">
-        <v>1631.631136735541</v>
+        <v>1696.840834517214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.450918850343311</v>
+        <v>0.4689402531548417</v>
       </c>
       <c r="G6" t="n">
-        <v>431.7982730992577</v>
+        <v>427.8527680828596</v>
       </c>
       <c r="H6" t="n">
-        <v>45.8843601575164</v>
+        <v>47.54152459831126</v>
       </c>
       <c r="I6" t="n">
-        <v>219.5934</v>
+        <v>738.8771</v>
       </c>
     </row>
     <row r="7">
@@ -778,28 +726,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>0.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1633.086596741191</v>
+        <v>1736.229786203676</v>
       </c>
       <c r="F7" t="n">
-        <v>0.451321082402808</v>
+        <v>0.4798258144871801</v>
       </c>
       <c r="G7" t="n">
-        <v>438.7302081093948</v>
+        <v>426.4287566540011</v>
       </c>
       <c r="H7" t="n">
-        <v>47.39375280600772</v>
+        <v>43.42155900394563</v>
       </c>
       <c r="I7" t="n">
-        <v>147.552</v>
+        <v>738.8771</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +755,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>16</v>
@@ -816,19 +764,19 @@
         <v>0.45</v>
       </c>
       <c r="E8" t="n">
-        <v>1648.948423684333</v>
+        <v>1742.053476923684</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4557046692371803</v>
+        <v>0.4814352541853431</v>
       </c>
       <c r="G8" t="n">
-        <v>438.872634378338</v>
+        <v>430.1882649605262</v>
       </c>
       <c r="H8" t="n">
-        <v>45.01407061321417</v>
+        <v>41.01910963202392</v>
       </c>
       <c r="I8" t="n">
-        <v>147.552</v>
+        <v>741.0981</v>
       </c>
     </row>
     <row r="9">
@@ -836,28 +784,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>0.45</v>
       </c>
       <c r="E9" t="n">
-        <v>1659.956956331859</v>
+        <v>1762.359171538601</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4587469958841949</v>
+        <v>0.4870469517467782</v>
       </c>
       <c r="G9" t="n">
-        <v>432.219916597818</v>
+        <v>428.1838648124625</v>
       </c>
       <c r="H9" t="n">
-        <v>43.43671413955228</v>
+        <v>40.69005468142417</v>
       </c>
       <c r="I9" t="n">
-        <v>219.5934</v>
+        <v>738.8771</v>
       </c>
     </row>
     <row r="10">
@@ -865,28 +813,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>1702.472323352153</v>
+        <v>1858.612963044279</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4704965757905156</v>
+        <v>0.5136477244519144</v>
       </c>
       <c r="G10" t="n">
-        <v>447.5223518980079</v>
+        <v>442.4616338614094</v>
       </c>
       <c r="H10" t="n">
-        <v>54.4633808994751</v>
+        <v>38.97994107455117</v>
       </c>
       <c r="I10" t="n">
-        <v>217.5576</v>
+        <v>741.0981</v>
       </c>
     </row>
     <row r="11">
@@ -894,318 +842,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>1724.527858515831</v>
+        <v>1861.918981834317</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4765918606473672</v>
+        <v>0.5145613783767838</v>
       </c>
       <c r="G11" t="n">
-        <v>435.7953017284703</v>
+        <v>438.8243848438888</v>
       </c>
       <c r="H11" t="n">
-        <v>49.72847177241587</v>
+        <v>39.12195505624732</v>
       </c>
       <c r="I11" t="n">
-        <v>217.5576</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1753.758233678002</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.4846699898681671</v>
-      </c>
-      <c r="G12" t="n">
-        <v>433.0485126176067</v>
-      </c>
-      <c r="H12" t="n">
-        <v>46.20989273272708</v>
-      </c>
-      <c r="I12" t="n">
-        <v>217.5576</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1767.188843747391</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.4883816837158431</v>
-      </c>
-      <c r="G13" t="n">
-        <v>455.0782437949665</v>
-      </c>
-      <c r="H13" t="n">
-        <v>55.87042245390593</v>
-      </c>
-      <c r="I13" t="n">
-        <v>147.5415</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" t="n">
-        <v>15</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1771.729311254256</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.4896364908484852</v>
-      </c>
-      <c r="G14" t="n">
-        <v>442.2057534790958</v>
-      </c>
-      <c r="H14" t="n">
-        <v>50.99486042213588</v>
-      </c>
-      <c r="I14" t="n">
-        <v>147.5415</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1771.807743712938</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.4896581665037864</v>
-      </c>
-      <c r="G15" t="n">
-        <v>434.1713581668672</v>
-      </c>
-      <c r="H15" t="n">
-        <v>43.86609210286657</v>
-      </c>
-      <c r="I15" t="n">
-        <v>217.5576</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1799.426968682379</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.497291037003862</v>
-      </c>
-      <c r="G16" t="n">
-        <v>438.517028026179</v>
-      </c>
-      <c r="H16" t="n">
-        <v>47.39949755777401</v>
-      </c>
-      <c r="I16" t="n">
-        <v>147.5415</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1814.935537435342</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.5015769971299648</v>
-      </c>
-      <c r="G17" t="n">
-        <v>439.7729581060469</v>
-      </c>
-      <c r="H17" t="n">
-        <v>45.25632939246051</v>
-      </c>
-      <c r="I17" t="n">
-        <v>147.5415</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>16</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1840.266043039844</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.5085773553657418</v>
-      </c>
-      <c r="G18" t="n">
-        <v>444.4523567885124</v>
-      </c>
-      <c r="H18" t="n">
-        <v>41.53383824148825</v>
-      </c>
-      <c r="I18" t="n">
-        <v>219.5934</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>16</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1852.796765714568</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5120403556329237</v>
-      </c>
-      <c r="G19" t="n">
-        <v>452.7988090254431</v>
-      </c>
-      <c r="H19" t="n">
-        <v>43.10378172798949</v>
-      </c>
-      <c r="I19" t="n">
-        <v>147.552</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1867.190072636094</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5160181011316264</v>
-      </c>
-      <c r="G20" t="n">
-        <v>442.1968949849231</v>
-      </c>
-      <c r="H20" t="n">
-        <v>42.31418858982504</v>
-      </c>
-      <c r="I20" t="n">
-        <v>217.5576</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>15</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1901.322786537956</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5254510445005047</v>
-      </c>
-      <c r="G21" t="n">
-        <v>446.326401401286</v>
-      </c>
-      <c r="H21" t="n">
-        <v>43.39630072123119</v>
-      </c>
-      <c r="I21" t="n">
-        <v>147.5415</v>
+        <v>738.8771</v>
       </c>
     </row>
   </sheetData>
@@ -1264,25 +922,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1679.657511378417</v>
+        <v>1728.950459284355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4641914566037251</v>
+        <v>0.4778140940365024</v>
       </c>
       <c r="F2" t="n">
-        <v>443.4065354497588</v>
+        <v>439.3296100409128</v>
       </c>
       <c r="G2" t="n">
-        <v>56.69277432394815</v>
+        <v>53.26589142884749</v>
       </c>
       <c r="H2" t="n">
-        <v>219.5934</v>
+        <v>741.0981</v>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -1355,19 +1013,19 @@
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1503.986624119089</v>
+        <v>1599.503818777609</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4156429135302885</v>
+        <v>0.442040119757678</v>
       </c>
       <c r="G2" t="n">
-        <v>437.5559240462001</v>
+        <v>434.6914419571065</v>
       </c>
       <c r="H2" t="n">
-        <v>54.14836824382113</v>
+        <v>52.27919078260592</v>
       </c>
       <c r="I2" t="n">
-        <v>219.5934</v>
+        <v>741.0981</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
+++ b/datasets/output/9574_1000__Dataset4_FirstWithOutl__kfinder__20260519_124033.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,25 +473,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1728.950459284355</v>
+        <v>1726.811934481259</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4778140940365024</v>
+        <v>0.4772230896581646</v>
       </c>
       <c r="F2" t="n">
-        <v>439.3296100409128</v>
+        <v>442.0080550298956</v>
       </c>
       <c r="G2" t="n">
-        <v>53.26589142884749</v>
+        <v>53.7240553920595</v>
       </c>
       <c r="H2" t="n">
-        <v>741.0981</v>
+        <v>594.2928000000001</v>
       </c>
     </row>
     <row r="3">
@@ -499,25 +499,181 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>1761.331187680383</v>
+        <v>1729.278018819321</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4867628573279584</v>
+        <v>0.4779046186444239</v>
       </c>
       <c r="F3" t="n">
-        <v>441.5117300156499</v>
+        <v>441.1256556500479</v>
       </c>
       <c r="G3" t="n">
-        <v>53.42096478776056</v>
+        <v>53.10878437079302</v>
       </c>
       <c r="H3" t="n">
-        <v>738.8771</v>
+        <v>708.3641</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1738.015432971072</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4803192972170355</v>
+      </c>
+      <c r="F4" t="n">
+        <v>446.9895245816234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>55.53682013442273</v>
+      </c>
+      <c r="H4" t="n">
+        <v>373.3658</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1738.20769014151</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4803724295582321</v>
+      </c>
+      <c r="F5" t="n">
+        <v>443.1982276552159</v>
+      </c>
+      <c r="G5" t="n">
+        <v>54.33874967341145</v>
+      </c>
+      <c r="H5" t="n">
+        <v>480.5021</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1746.895598547838</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4827734266845235</v>
+      </c>
+      <c r="F6" t="n">
+        <v>444.1545284721106</v>
+      </c>
+      <c r="G6" t="n">
+        <v>55.17728331414013</v>
+      </c>
+      <c r="H6" t="n">
+        <v>479.5889</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1772.78983717981</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4899295786183515</v>
+      </c>
+      <c r="F7" t="n">
+        <v>445.9180952791311</v>
+      </c>
+      <c r="G7" t="n">
+        <v>56.19501885896203</v>
+      </c>
+      <c r="H7" t="n">
+        <v>370.1601</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1773.818428308298</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4902138408628556</v>
+      </c>
+      <c r="F8" t="n">
+        <v>444.9439643702196</v>
+      </c>
+      <c r="G8" t="n">
+        <v>54.55620157927764</v>
+      </c>
+      <c r="H8" t="n">
+        <v>593.2342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1774.667198428073</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4904484076334924</v>
+      </c>
+      <c r="F9" t="n">
+        <v>443.2063188286511</v>
+      </c>
+      <c r="G9" t="n">
+        <v>54.12601549993143</v>
+      </c>
+      <c r="H9" t="n">
+        <v>708.3019</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -590,19 +746,19 @@
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1599.503818777609</v>
+        <v>1586.514870417418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.442040119757678</v>
+        <v>0.4384504838835649</v>
       </c>
       <c r="G2" t="n">
-        <v>434.6914419571065</v>
+        <v>443.3286955537119</v>
       </c>
       <c r="H2" t="n">
-        <v>52.27919078260592</v>
+        <v>54.33103416182665</v>
       </c>
       <c r="I2" t="n">
-        <v>741.0981</v>
+        <v>373.3658</v>
       </c>
     </row>
     <row r="3">
@@ -610,28 +766,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1656.106205406015</v>
+        <v>1592.10883323548</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4576827993624775</v>
+        <v>0.4399964358000198</v>
       </c>
       <c r="G3" t="n">
-        <v>437.651219973989</v>
+        <v>437.295880580839</v>
       </c>
       <c r="H3" t="n">
-        <v>52.09846348965927</v>
+        <v>52.90536873511472</v>
       </c>
       <c r="I3" t="n">
-        <v>738.8771</v>
+        <v>594.2928000000001</v>
       </c>
     </row>
     <row r="4">
@@ -639,28 +795,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
         <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1657.631874178728</v>
+        <v>1599.840611154902</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4581044343714618</v>
+        <v>0.4421331959610884</v>
       </c>
       <c r="G4" t="n">
-        <v>427.3678013566716</v>
+        <v>436.5474305256212</v>
       </c>
       <c r="H4" t="n">
-        <v>47.64618322755457</v>
+        <v>52.52579552437621</v>
       </c>
       <c r="I4" t="n">
-        <v>741.0981</v>
+        <v>708.3641</v>
       </c>
     </row>
     <row r="5">
@@ -668,28 +824,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1690.728978533481</v>
+        <v>1610.101971389695</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4672511758802055</v>
+        <v>0.4449690334588264</v>
       </c>
       <c r="G5" t="n">
-        <v>427.2500854495922</v>
+        <v>441.2179158146578</v>
       </c>
       <c r="H5" t="n">
-        <v>43.74693319680208</v>
+        <v>53.53782015088026</v>
       </c>
       <c r="I5" t="n">
-        <v>741.0981</v>
+        <v>480.5021</v>
       </c>
     </row>
     <row r="6">
@@ -697,28 +853,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E6" t="n">
-        <v>1696.840834517214</v>
+        <v>1623.112379556721</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4689402531548417</v>
+        <v>0.4485645999818521</v>
       </c>
       <c r="G6" t="n">
-        <v>427.8527680828596</v>
+        <v>440.8548805391516</v>
       </c>
       <c r="H6" t="n">
-        <v>47.54152459831126</v>
+        <v>53.95405218157803</v>
       </c>
       <c r="I6" t="n">
-        <v>738.8771</v>
+        <v>479.5889</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +882,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E7" t="n">
-        <v>1736.229786203676</v>
+        <v>1642.900177655025</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4798258144871801</v>
+        <v>0.4540331712590372</v>
       </c>
       <c r="G7" t="n">
-        <v>426.4287566540011</v>
+        <v>429.7239997167848</v>
       </c>
       <c r="H7" t="n">
-        <v>43.42155900394563</v>
+        <v>48.336854709498</v>
       </c>
       <c r="I7" t="n">
-        <v>738.8771</v>
+        <v>594.2928000000001</v>
       </c>
     </row>
     <row r="8">
@@ -755,28 +911,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E8" t="n">
-        <v>1742.053476923684</v>
+        <v>1652.114360520759</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4814352541853431</v>
+        <v>0.4565796100043668</v>
       </c>
       <c r="G8" t="n">
-        <v>430.1882649605262</v>
+        <v>428.9362007783498</v>
       </c>
       <c r="H8" t="n">
-        <v>41.01910963202392</v>
+        <v>47.82456891165023</v>
       </c>
       <c r="I8" t="n">
-        <v>741.0981</v>
+        <v>708.3641</v>
       </c>
     </row>
     <row r="9">
@@ -784,28 +940,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
-        <v>1762.359171538601</v>
+        <v>1655.598743636036</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4870469517467782</v>
+        <v>0.4575425568329251</v>
       </c>
       <c r="G9" t="n">
-        <v>428.1838648124625</v>
+        <v>442.9923136780423</v>
       </c>
       <c r="H9" t="n">
-        <v>40.69005468142417</v>
+        <v>53.83689069565117</v>
       </c>
       <c r="I9" t="n">
-        <v>738.8771</v>
+        <v>370.1601</v>
       </c>
     </row>
     <row r="10">
@@ -813,28 +969,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="E10" t="n">
-        <v>1858.612963044279</v>
+        <v>1656.775855312644</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5136477244519144</v>
+        <v>0.4578678643316554</v>
       </c>
       <c r="G10" t="n">
-        <v>442.4616338614094</v>
+        <v>435.2448808643943</v>
       </c>
       <c r="H10" t="n">
-        <v>38.97994107455117</v>
+        <v>49.52635180261643</v>
       </c>
       <c r="I10" t="n">
-        <v>741.0981</v>
+        <v>373.3658</v>
       </c>
     </row>
     <row r="11">
@@ -842,28 +998,898 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1663.955446021491</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4598520216056126</v>
+      </c>
+      <c r="G11" t="n">
+        <v>441.1271371752181</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53.30086016353883</v>
+      </c>
+      <c r="I11" t="n">
+        <v>593.2342</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
-        <v>15</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1666.160269442977</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.460461348321708</v>
+      </c>
+      <c r="G12" t="n">
+        <v>429.325172892466</v>
+      </c>
+      <c r="H12" t="n">
+        <v>49.23309295475381</v>
+      </c>
+      <c r="I12" t="n">
+        <v>479.5889</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1668.337292227059</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4610629920320221</v>
+      </c>
+      <c r="G13" t="n">
+        <v>439.5679284462493</v>
+      </c>
+      <c r="H13" t="n">
+        <v>52.83621063275097</v>
+      </c>
+      <c r="I13" t="n">
+        <v>708.3019</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1671.31410868179</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4618856673433892</v>
+      </c>
+      <c r="G14" t="n">
+        <v>433.2406651650884</v>
+      </c>
+      <c r="H14" t="n">
+        <v>48.83536361420222</v>
+      </c>
+      <c r="I14" t="n">
+        <v>480.5021</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1677.357243083985</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4635557526682869</v>
+      </c>
+      <c r="G15" t="n">
+        <v>427.1362645230041</v>
+      </c>
+      <c r="H15" t="n">
+        <v>44.23207189455729</v>
+      </c>
+      <c r="I15" t="n">
+        <v>594.2928000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1685.820174930351</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4658945750974373</v>
+      </c>
+      <c r="G16" t="n">
+        <v>426.6540833174249</v>
+      </c>
+      <c r="H16" t="n">
+        <v>43.88940501831969</v>
+      </c>
+      <c r="I16" t="n">
+        <v>708.3641</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1693.091920304793</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4679042003064736</v>
+      </c>
+      <c r="G17" t="n">
+        <v>430.5513612725958</v>
+      </c>
+      <c r="H17" t="n">
+        <v>49.04353903767846</v>
+      </c>
+      <c r="I17" t="n">
+        <v>370.1601</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1697.255273293056</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.469054787777363</v>
+      </c>
+      <c r="G18" t="n">
+        <v>429.6584184531577</v>
+      </c>
+      <c r="H18" t="n">
+        <v>48.64139773335609</v>
+      </c>
+      <c r="I18" t="n">
+        <v>593.2342</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1700.756993787945</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4700225259776393</v>
+      </c>
+      <c r="G19" t="n">
+        <v>427.0261403102008</v>
+      </c>
+      <c r="H19" t="n">
+        <v>44.57927291073304</v>
+      </c>
+      <c r="I19" t="n">
+        <v>479.5889</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1702.722623037997</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4705657488064265</v>
+      </c>
+      <c r="G20" t="n">
+        <v>433.2944308249381</v>
+      </c>
+      <c r="H20" t="n">
+        <v>45.17351771157925</v>
+      </c>
+      <c r="I20" t="n">
+        <v>373.3658</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1704.97844706339</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4711891700890959</v>
+      </c>
+      <c r="G21" t="n">
+        <v>429.247290205192</v>
+      </c>
+      <c r="H21" t="n">
+        <v>48.15347508944312</v>
+      </c>
+      <c r="I21" t="n">
+        <v>708.3019</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1714.298172519153</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4737647766667172</v>
+      </c>
+      <c r="G22" t="n">
+        <v>431.5523073119065</v>
+      </c>
+      <c r="H22" t="n">
+        <v>44.40482063704977</v>
+      </c>
+      <c r="I22" t="n">
+        <v>480.5021</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1716.762416683864</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.4744457971012377</v>
+      </c>
+      <c r="G23" t="n">
+        <v>429.6938245846556</v>
+      </c>
+      <c r="H23" t="n">
+        <v>41.64499406611361</v>
+      </c>
+      <c r="I23" t="n">
+        <v>594.2928000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1724.970918986014</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.4767143051836045</v>
+      </c>
+      <c r="G24" t="n">
+        <v>429.8409880708349</v>
+      </c>
+      <c r="H24" t="n">
+        <v>42.0489792785545</v>
+      </c>
+      <c r="I24" t="n">
+        <v>479.5889</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1728.37069816148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4776538708015354</v>
+      </c>
+      <c r="G25" t="n">
+        <v>429.604062960227</v>
+      </c>
+      <c r="H25" t="n">
+        <v>41.27902530385052</v>
+      </c>
+      <c r="I25" t="n">
+        <v>708.3641</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>15</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1728.932377491403</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4778090969381346</v>
+      </c>
+      <c r="G26" t="n">
+        <v>428.9658021199043</v>
+      </c>
+      <c r="H26" t="n">
+        <v>45.27963134947574</v>
+      </c>
+      <c r="I26" t="n">
+        <v>370.1601</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>15</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1732.699919205681</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4788502976974077</v>
+      </c>
+      <c r="G27" t="n">
+        <v>428.5876167866539</v>
+      </c>
+      <c r="H27" t="n">
+        <v>44.38488997292416</v>
+      </c>
+      <c r="I27" t="n">
+        <v>593.2342</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>16</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1739.691626408708</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.4807825313395248</v>
+      </c>
+      <c r="G28" t="n">
+        <v>434.9818629119711</v>
+      </c>
+      <c r="H28" t="n">
+        <v>42.69769044726026</v>
+      </c>
+      <c r="I28" t="n">
+        <v>373.3658</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1743.757737316526</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4819062449134088</v>
+      </c>
+      <c r="G29" t="n">
+        <v>427.6223317596062</v>
+      </c>
+      <c r="H29" t="n">
+        <v>43.99247316561931</v>
+      </c>
+      <c r="I29" t="n">
+        <v>708.3019</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>16</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1746.376806806732</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.4826300529953358</v>
+      </c>
+      <c r="G30" t="n">
+        <v>433.4371087823572</v>
+      </c>
+      <c r="H30" t="n">
+        <v>41.95545030687548</v>
+      </c>
+      <c r="I30" t="n">
+        <v>480.5021</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1752.505376959937</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.4843237494108507</v>
+      </c>
+      <c r="G31" t="n">
+        <v>431.5390847348116</v>
+      </c>
+      <c r="H31" t="n">
+        <v>42.80660791621705</v>
+      </c>
+      <c r="I31" t="n">
+        <v>370.1601</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1757.446439321398</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4856892652491682</v>
+      </c>
+      <c r="G32" t="n">
+        <v>430.4201014984368</v>
+      </c>
+      <c r="H32" t="n">
+        <v>41.69339995195382</v>
+      </c>
+      <c r="I32" t="n">
+        <v>593.2342</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1770.396404317423</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4892681276504318</v>
+      </c>
+      <c r="G33" t="n">
+        <v>429.7227083855843</v>
+      </c>
+      <c r="H33" t="n">
+        <v>41.27253742592411</v>
+      </c>
+      <c r="I33" t="n">
+        <v>708.3019</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>15</v>
+      </c>
+      <c r="D34" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11" t="n">
-        <v>1861.918981834317</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.5145613783767838</v>
-      </c>
-      <c r="G11" t="n">
-        <v>438.8243848438888</v>
-      </c>
-      <c r="H11" t="n">
-        <v>39.12195505624732</v>
-      </c>
-      <c r="I11" t="n">
-        <v>738.8771</v>
+      <c r="E34" t="n">
+        <v>1831.695754211536</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5062088636775391</v>
+      </c>
+      <c r="G34" t="n">
+        <v>439.7869697137546</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40.61650278178875</v>
+      </c>
+      <c r="I34" t="n">
+        <v>479.5889</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1834.421388804756</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5069621221742419</v>
+      </c>
+      <c r="G35" t="n">
+        <v>439.5883145456765</v>
+      </c>
+      <c r="H35" t="n">
+        <v>41.38496230586514</v>
+      </c>
+      <c r="I35" t="n">
+        <v>370.1601</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1840.262581365702</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5085763986947829</v>
+      </c>
+      <c r="G36" t="n">
+        <v>440.6279736132072</v>
+      </c>
+      <c r="H36" t="n">
+        <v>39.6773533148002</v>
+      </c>
+      <c r="I36" t="n">
+        <v>594.2928000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1847.365528597156</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5105393747176997</v>
+      </c>
+      <c r="G37" t="n">
+        <v>440.6605641862674</v>
+      </c>
+      <c r="H37" t="n">
+        <v>39.29974494805188</v>
+      </c>
+      <c r="I37" t="n">
+        <v>708.3641</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1854.29000013253</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5124530270583953</v>
+      </c>
+      <c r="G38" t="n">
+        <v>440.4596811097041</v>
+      </c>
+      <c r="H38" t="n">
+        <v>40.05263557856695</v>
+      </c>
+      <c r="I38" t="n">
+        <v>593.2342</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>15</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1868.249002062344</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5163107476917027</v>
+      </c>
+      <c r="G39" t="n">
+        <v>439.8210501267046</v>
+      </c>
+      <c r="H39" t="n">
+        <v>39.6432161507444</v>
+      </c>
+      <c r="I39" t="n">
+        <v>708.3019</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1885.303627815264</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5210239773331328</v>
+      </c>
+      <c r="G40" t="n">
+        <v>444.9012930245701</v>
+      </c>
+      <c r="H40" t="n">
+        <v>40.30085415214542</v>
+      </c>
+      <c r="I40" t="n">
+        <v>480.5021</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1888.472173861584</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5218996391835957</v>
+      </c>
+      <c r="G41" t="n">
+        <v>446.6977095614628</v>
+      </c>
+      <c r="H41" t="n">
+        <v>41.06267891051363</v>
+      </c>
+      <c r="I41" t="n">
+        <v>373.3658</v>
       </c>
     </row>
   </sheetData>
@@ -922,25 +1948,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>1728.950459284355</v>
+        <v>1726.811934481259</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4778140940365024</v>
+        <v>0.4772230896581646</v>
       </c>
       <c r="F2" t="n">
-        <v>439.3296100409128</v>
+        <v>442.0080550298956</v>
       </c>
       <c r="G2" t="n">
-        <v>53.26589142884749</v>
+        <v>53.7240553920595</v>
       </c>
       <c r="H2" t="n">
-        <v>741.0981</v>
+        <v>594.2928000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1004,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -1013,19 +2039,19 @@
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1599.503818777609</v>
+        <v>1586.514870417418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.442040119757678</v>
+        <v>0.4384504838835649</v>
       </c>
       <c r="G2" t="n">
-        <v>434.6914419571065</v>
+        <v>443.3286955537119</v>
       </c>
       <c r="H2" t="n">
-        <v>52.27919078260592</v>
+        <v>54.33103416182665</v>
       </c>
       <c r="I2" t="n">
-        <v>741.0981</v>
+        <v>373.3658</v>
       </c>
     </row>
   </sheetData>
